--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v2/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v2/EVAL_SUMMARY.xlsx
@@ -544,13 +544,13 @@
         <v>0.375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="3">
@@ -603,13 +603,13 @@
         <v>0.375</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="4">
@@ -662,13 +662,13 @@
         <v>0.375</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
   </sheetData>
@@ -787,13 +787,13 @@
         <v>0.375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
       <c r="J2" t="n">
         <v>756</v>
